--- a/base_clima/temperaturas_2025.xlsx
+++ b/base_clima/temperaturas_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pmilhopetrolina\Desktop\GDU 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apps\calculadora_gdu\CalculadoraGDU\base_clima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82820C1-8B26-41BC-8138-B7CAA6966572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49DFEAE8-BD71-480B-A5DF-F19E33DB538B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fonte  Estação Terra Nova Temp." sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
   <si>
     <t>data</t>
   </si>
@@ -68,12 +68,157 @@
   <si>
     <t>GDM TERRA NOVA PETROLINA</t>
   </si>
+  <si>
+    <t>26/10/2025</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>28/10/2025</t>
+  </si>
+  <si>
+    <t>29/10/2025</t>
+  </si>
+  <si>
+    <t>30/10/2025</t>
+  </si>
+  <si>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>02/11/2025</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>08/11/2025</t>
+  </si>
+  <si>
+    <t>09/11/2025</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
+    <t>13/11/2025</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>15/11/2025</t>
+  </si>
+  <si>
+    <t>16/11/2025</t>
+  </si>
+  <si>
+    <t>17/11/2025</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>22/11/2025</t>
+  </si>
+  <si>
+    <t>23/11/2025</t>
+  </si>
+  <si>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>29/11/2025</t>
+  </si>
+  <si>
+    <t>30/11/2025</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>04/12/2025</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>06/12/2025</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
+  </si>
+  <si>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>10/12/2025</t>
+  </si>
+  <si>
+    <t>11/12/2025</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -85,6 +230,16 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,10 +277,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -167,9 +323,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -501,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA348"/>
+  <dimension ref="A1:AA378"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="6" customWidth="1"/>
@@ -541,7 +704,7 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <f>(B2+C2)/2 -10</f>
+        <f t="shared" ref="D2:D65" si="0">(B2+C2)/2 -10</f>
         <v>14.600000000000001</v>
       </c>
     </row>
@@ -556,7 +719,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <f>(B3+C3)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
     </row>
@@ -571,7 +734,7 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <f>(B4+C4)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.3</v>
       </c>
     </row>
@@ -586,7 +749,7 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <f>(B5+C5)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.3</v>
       </c>
     </row>
@@ -601,7 +764,7 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <f>(B6+C6)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.45</v>
       </c>
     </row>
@@ -616,7 +779,7 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <f>(B7+C7)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.100000000000001</v>
       </c>
     </row>
@@ -631,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <f>(B8+C8)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.2</v>
       </c>
     </row>
@@ -646,7 +809,7 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <f>(B9+C9)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.55</v>
       </c>
       <c r="F9" s="2"/>
@@ -662,7 +825,7 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <f>(B10+C10)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.2</v>
       </c>
       <c r="F10" s="2"/>
@@ -678,7 +841,7 @@
         <v>30</v>
       </c>
       <c r="D11">
-        <f>(B11+C11)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.399999999999999</v>
       </c>
     </row>
@@ -693,7 +856,7 @@
         <v>30</v>
       </c>
       <c r="D12">
-        <f>(B12+C12)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.350000000000001</v>
       </c>
     </row>
@@ -708,7 +871,7 @@
         <v>30</v>
       </c>
       <c r="D13">
-        <f>(B13+C13)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.05</v>
       </c>
     </row>
@@ -723,7 +886,7 @@
         <v>30</v>
       </c>
       <c r="D14">
-        <f>(B14+C14)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.7</v>
       </c>
     </row>
@@ -738,7 +901,7 @@
         <v>30</v>
       </c>
       <c r="D15">
-        <f>(B15+C15)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
     </row>
@@ -753,7 +916,7 @@
         <v>30</v>
       </c>
       <c r="D16">
-        <f>(B16+C16)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.149999999999999</v>
       </c>
     </row>
@@ -768,7 +931,7 @@
         <v>30</v>
       </c>
       <c r="D17">
-        <f>(B17+C17)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.3</v>
       </c>
     </row>
@@ -783,7 +946,7 @@
         <v>30</v>
       </c>
       <c r="D18">
-        <f>(B18+C18)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.149999999999999</v>
       </c>
     </row>
@@ -798,7 +961,7 @@
         <v>30</v>
       </c>
       <c r="D19">
-        <f>(B19+C19)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.95</v>
       </c>
     </row>
@@ -813,7 +976,7 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <f>(B20+C20)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.8</v>
       </c>
     </row>
@@ -828,7 +991,7 @@
         <v>30</v>
       </c>
       <c r="D21">
-        <f>(B21+C21)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -843,7 +1006,7 @@
         <v>30</v>
       </c>
       <c r="D22">
-        <f>(B22+C22)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.899999999999999</v>
       </c>
     </row>
@@ -858,7 +1021,7 @@
         <v>30</v>
       </c>
       <c r="D23">
-        <f>(B23+C23)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -873,7 +1036,7 @@
         <v>30</v>
       </c>
       <c r="D24">
-        <f>(B24+C24)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.149999999999999</v>
       </c>
     </row>
@@ -888,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="D25">
-        <f>(B25+C25)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.55</v>
       </c>
     </row>
@@ -903,7 +1066,7 @@
         <v>30</v>
       </c>
       <c r="D26">
-        <f>(B26+C26)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.55</v>
       </c>
     </row>
@@ -918,7 +1081,7 @@
         <v>30</v>
       </c>
       <c r="D27">
-        <f>(B27+C27)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.05</v>
       </c>
     </row>
@@ -933,7 +1096,7 @@
         <v>30</v>
       </c>
       <c r="D28">
-        <f>(B28+C28)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.2</v>
       </c>
     </row>
@@ -948,7 +1111,7 @@
         <v>30</v>
       </c>
       <c r="D29">
-        <f>(B29+C29)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.95</v>
       </c>
     </row>
@@ -963,7 +1126,7 @@
         <v>30</v>
       </c>
       <c r="D30">
-        <f>(B30+C30)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>16.55</v>
       </c>
     </row>
@@ -978,7 +1141,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <f>(B31+C31)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>16.149999999999999</v>
       </c>
     </row>
@@ -993,7 +1156,7 @@
         <v>21.6</v>
       </c>
       <c r="D32">
-        <f>(B32+C32)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>9.3000000000000007</v>
       </c>
     </row>
@@ -1008,7 +1171,7 @@
         <v>30</v>
       </c>
       <c r="D33">
-        <f>(B33+C33)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
@@ -1023,7 +1186,7 @@
         <v>29.5</v>
       </c>
       <c r="D34">
-        <f>(B34+C34)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.75</v>
       </c>
     </row>
@@ -1038,7 +1201,7 @@
         <v>30</v>
       </c>
       <c r="D35">
-        <f>(B35+C35)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
     </row>
@@ -1053,7 +1216,7 @@
         <v>30</v>
       </c>
       <c r="D36">
-        <f>(B36+C36)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.5</v>
       </c>
     </row>
@@ -1068,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="D37">
-        <f>(B37+C37)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
     </row>
@@ -1083,7 +1246,7 @@
         <v>30</v>
       </c>
       <c r="D38">
-        <f>(B38+C38)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
     </row>
@@ -1098,7 +1261,7 @@
         <v>30</v>
       </c>
       <c r="D39">
-        <f>(B39+C39)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -1113,7 +1276,7 @@
         <v>30</v>
       </c>
       <c r="D40">
-        <f>(B40+C40)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -1128,7 +1291,7 @@
         <v>30</v>
       </c>
       <c r="D41">
-        <f>(B41+C41)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.5</v>
       </c>
     </row>
@@ -1143,7 +1306,7 @@
         <v>30</v>
       </c>
       <c r="D42">
-        <f>(B42+C42)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
     </row>
@@ -1158,7 +1321,7 @@
         <v>29.2</v>
       </c>
       <c r="D43">
-        <f>(B43+C43)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.100000000000001</v>
       </c>
     </row>
@@ -1173,7 +1336,7 @@
         <v>29.7</v>
       </c>
       <c r="D44">
-        <f>(B44+C44)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>12.850000000000001</v>
       </c>
     </row>
@@ -1188,7 +1351,7 @@
         <v>29</v>
       </c>
       <c r="D45">
-        <f>(B45+C45)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
@@ -1203,7 +1366,7 @@
         <v>28.9</v>
       </c>
       <c r="D46">
-        <f>(B46+C46)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.45</v>
       </c>
     </row>
@@ -1218,7 +1381,7 @@
         <v>26.6</v>
       </c>
       <c r="D47">
-        <f>(B47+C47)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>11.8</v>
       </c>
     </row>
@@ -1233,7 +1396,7 @@
         <v>28.6</v>
       </c>
       <c r="D48">
-        <f>(B48+C48)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
     </row>
@@ -1248,7 +1411,7 @@
         <v>28.6</v>
       </c>
       <c r="D49">
-        <f>(B49+C49)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.8</v>
       </c>
     </row>
@@ -1263,7 +1426,7 @@
         <v>29.1</v>
       </c>
       <c r="D50">
-        <f>(B50+C50)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.55</v>
       </c>
     </row>
@@ -1278,7 +1441,7 @@
         <v>29.7</v>
       </c>
       <c r="D51">
-        <f>(B51+C51)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.850000000000001</v>
       </c>
     </row>
@@ -1293,7 +1456,7 @@
         <v>26.5</v>
       </c>
       <c r="D52">
-        <f>(B52+C52)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>12.75</v>
       </c>
     </row>
@@ -1308,7 +1471,7 @@
         <v>27.7</v>
       </c>
       <c r="D53">
-        <f>(B53+C53)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>12.350000000000001</v>
       </c>
     </row>
@@ -1323,7 +1486,7 @@
         <v>28.2</v>
       </c>
       <c r="D54">
-        <f>(B54+C54)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.100000000000001</v>
       </c>
     </row>
@@ -1338,7 +1501,7 @@
         <v>29.7</v>
       </c>
       <c r="D55">
-        <f>(B55+C55)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.350000000000001</v>
       </c>
     </row>
@@ -1353,7 +1516,7 @@
         <v>27.7</v>
       </c>
       <c r="D56">
-        <f>(B56+C56)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>11.850000000000001</v>
       </c>
     </row>
@@ -1368,7 +1531,7 @@
         <v>28.2</v>
       </c>
       <c r="D57">
-        <f>(B57+C57)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.100000000000001</v>
       </c>
     </row>
@@ -1383,7 +1546,7 @@
         <v>29.1</v>
       </c>
       <c r="D58">
-        <f>(B58+C58)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.55</v>
       </c>
     </row>
@@ -1398,7 +1561,7 @@
         <v>27.2</v>
       </c>
       <c r="D59">
-        <f>(B59+C59)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.600000000000001</v>
       </c>
     </row>
@@ -1413,7 +1576,7 @@
         <v>26.8</v>
       </c>
       <c r="D60">
-        <f>(B60+C60)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.399999999999999</v>
       </c>
     </row>
@@ -1428,7 +1591,7 @@
         <v>28</v>
       </c>
       <c r="D61">
-        <f>(B61+C61)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
@@ -1443,7 +1606,7 @@
         <v>29</v>
       </c>
       <c r="D62">
-        <f>(B62+C62)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -1458,7 +1621,7 @@
         <v>29.5</v>
       </c>
       <c r="D63">
-        <f>(B63+C63)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>13.75</v>
       </c>
     </row>
@@ -1473,7 +1636,7 @@
         <v>29.2</v>
       </c>
       <c r="D64">
-        <f>(B64+C64)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>14.600000000000001</v>
       </c>
     </row>
@@ -1488,7 +1651,7 @@
         <v>30</v>
       </c>
       <c r="D65">
-        <f>(B65+C65)/2 -10</f>
+        <f t="shared" si="0"/>
         <v>15.5</v>
       </c>
     </row>
@@ -1503,7 +1666,7 @@
         <v>30</v>
       </c>
       <c r="D66">
-        <f>(B66+C66)/2 -10</f>
+        <f t="shared" ref="D66:D129" si="1">(B66+C66)/2 -10</f>
         <v>13.5</v>
       </c>
     </row>
@@ -1518,7 +1681,7 @@
         <v>29.2</v>
       </c>
       <c r="D67">
-        <f>(B67+C67)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>12.600000000000001</v>
       </c>
     </row>
@@ -1533,7 +1696,7 @@
         <v>30</v>
       </c>
       <c r="D68">
-        <f>(B68+C68)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1548,7 +1711,7 @@
         <v>30</v>
       </c>
       <c r="D69">
-        <f>(B69+C69)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1563,7 +1726,7 @@
         <v>28.7</v>
       </c>
       <c r="D70">
-        <f>(B70+C70)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -1578,7 +1741,7 @@
         <v>28.8</v>
       </c>
       <c r="D71">
-        <f>(B71+C71)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>13.899999999999999</v>
       </c>
     </row>
@@ -1593,7 +1756,7 @@
         <v>29.7</v>
       </c>
       <c r="D72">
-        <f>(B72+C72)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -1608,7 +1771,7 @@
         <v>28.6</v>
       </c>
       <c r="D73">
-        <f>(B73+C73)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.3</v>
       </c>
     </row>
@@ -1623,7 +1786,7 @@
         <v>28.6</v>
       </c>
       <c r="D74">
-        <f>(B74+C74)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>13.8</v>
       </c>
     </row>
@@ -1638,7 +1801,7 @@
         <v>26</v>
       </c>
       <c r="D75">
-        <f>(B75+C75)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
     </row>
@@ -1653,7 +1816,7 @@
         <v>25.8</v>
       </c>
       <c r="D76">
-        <f>(B76+C76)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>12.899999999999999</v>
       </c>
     </row>
@@ -1668,7 +1831,7 @@
         <v>27.5</v>
       </c>
       <c r="D77">
-        <f>(B77+C77)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.25</v>
       </c>
     </row>
@@ -1683,7 +1846,7 @@
         <v>30</v>
       </c>
       <c r="D78">
-        <f>(B78+C78)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1698,7 +1861,7 @@
         <v>30</v>
       </c>
       <c r="D79">
-        <f>(B79+C79)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1713,7 +1876,7 @@
         <v>30</v>
       </c>
       <c r="D80">
-        <f>(B80+C80)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1728,7 +1891,7 @@
         <v>30</v>
       </c>
       <c r="D81">
-        <f>(B81+C81)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1743,7 +1906,7 @@
         <v>29.3</v>
       </c>
       <c r="D82">
-        <f>(B82+C82)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>13.649999999999999</v>
       </c>
     </row>
@@ -1758,7 +1921,7 @@
         <v>30</v>
       </c>
       <c r="D83">
-        <f>(B83+C83)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.5</v>
       </c>
     </row>
@@ -1773,7 +1936,7 @@
         <v>30</v>
       </c>
       <c r="D84">
-        <f>(B84+C84)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1788,7 +1951,7 @@
         <v>30</v>
       </c>
       <c r="D85">
-        <f>(B85+C85)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1803,7 +1966,7 @@
         <v>30</v>
       </c>
       <c r="D86">
-        <f>(B86+C86)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.5</v>
       </c>
     </row>
@@ -1818,7 +1981,7 @@
         <v>30</v>
       </c>
       <c r="D87">
-        <f>(B87+C87)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1833,7 +1996,7 @@
         <v>30</v>
       </c>
       <c r="D88">
-        <f>(B88+C88)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1848,7 +2011,7 @@
         <v>30</v>
       </c>
       <c r="D89">
-        <f>(B89+C89)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1863,7 +2026,7 @@
         <v>30</v>
       </c>
       <c r="D90">
-        <f>(B90+C90)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -1878,7 +2041,7 @@
         <v>30</v>
       </c>
       <c r="D91">
-        <f>(B91+C91)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1893,7 +2056,7 @@
         <v>30</v>
       </c>
       <c r="D92">
-        <f>(B92+C92)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1908,7 +2071,7 @@
         <v>30</v>
       </c>
       <c r="D93">
-        <f>(B93+C93)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1923,7 +2086,7 @@
         <v>30</v>
       </c>
       <c r="D94">
-        <f>(B94+C94)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1938,7 +2101,7 @@
         <v>30</v>
       </c>
       <c r="D95">
-        <f>(B95+C95)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1953,7 +2116,7 @@
         <v>28.6</v>
       </c>
       <c r="D96">
-        <f>(B96+C96)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.8</v>
       </c>
     </row>
@@ -1968,7 +2131,7 @@
         <v>30</v>
       </c>
       <c r="D97">
-        <f>(B97+C97)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -1983,7 +2146,7 @@
         <v>30</v>
       </c>
       <c r="D98">
-        <f>(B98+C98)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.5</v>
       </c>
     </row>
@@ -1998,7 +2161,7 @@
         <v>28.4</v>
       </c>
       <c r="D99">
-        <f>(B99+C99)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.2</v>
       </c>
     </row>
@@ -2013,7 +2176,7 @@
         <v>28.2</v>
       </c>
       <c r="D100">
-        <f>(B100+C100)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15.100000000000001</v>
       </c>
     </row>
@@ -2028,7 +2191,7 @@
         <v>29</v>
       </c>
       <c r="D101">
-        <f>(B101+C101)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>13.5</v>
       </c>
     </row>
@@ -2043,7 +2206,7 @@
         <v>29.9</v>
       </c>
       <c r="D102">
-        <f>(B102+C102)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.95</v>
       </c>
     </row>
@@ -2058,7 +2221,7 @@
         <v>28.6</v>
       </c>
       <c r="D103">
-        <f>(B103+C103)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.8</v>
       </c>
     </row>
@@ -2073,7 +2236,7 @@
         <v>29.3</v>
       </c>
       <c r="D104">
-        <f>(B104+C104)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.149999999999999</v>
       </c>
     </row>
@@ -2088,7 +2251,7 @@
         <v>30</v>
       </c>
       <c r="D105">
-        <f>(B105+C105)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -2103,7 +2266,7 @@
         <v>29.9</v>
       </c>
       <c r="D106">
-        <f>(B106+C106)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.45</v>
       </c>
     </row>
@@ -2118,7 +2281,7 @@
         <v>28.2</v>
       </c>
       <c r="D107">
-        <f>(B107+C107)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.100000000000001</v>
       </c>
     </row>
@@ -2133,7 +2296,7 @@
         <v>28.6</v>
       </c>
       <c r="D108">
-        <f>(B108+C108)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>13.8</v>
       </c>
     </row>
@@ -2148,7 +2311,7 @@
         <v>29.7</v>
       </c>
       <c r="D109">
-        <f>(B109+C109)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16.350000000000001</v>
       </c>
     </row>
@@ -2163,7 +2326,7 @@
         <v>30</v>
       </c>
       <c r="D110">
-        <f>(B110+C110)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -2178,7 +2341,7 @@
         <v>30</v>
       </c>
       <c r="D111">
-        <f>(B111+C111)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2193,7 +2356,7 @@
         <v>30</v>
       </c>
       <c r="D112">
-        <f>(B112+C112)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2208,7 +2371,7 @@
         <v>30</v>
       </c>
       <c r="D113">
-        <f>(B113+C113)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2223,7 +2386,7 @@
         <v>30</v>
       </c>
       <c r="D114">
-        <f>(B114+C114)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2238,7 +2401,7 @@
         <v>30</v>
       </c>
       <c r="D115">
-        <f>(B115+C115)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2253,7 +2416,7 @@
         <v>30</v>
       </c>
       <c r="D116">
-        <f>(B116+C116)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2268,7 +2431,7 @@
         <v>29.2</v>
       </c>
       <c r="D117">
-        <f>(B117+C117)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>14.600000000000001</v>
       </c>
     </row>
@@ -2283,7 +2446,7 @@
         <v>30</v>
       </c>
       <c r="D118">
-        <f>(B118+C118)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2298,7 +2461,7 @@
         <v>30</v>
       </c>
       <c r="D119">
-        <f>(B119+C119)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -2313,7 +2476,7 @@
         <v>30</v>
       </c>
       <c r="D120">
-        <f>(B120+C120)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2328,7 +2491,7 @@
         <v>30</v>
       </c>
       <c r="D121">
-        <f>(B121+C121)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16.5</v>
       </c>
     </row>
@@ -2343,7 +2506,7 @@
         <v>30</v>
       </c>
       <c r="D122">
-        <f>(B122+C122)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -2358,7 +2521,7 @@
         <v>30</v>
       </c>
       <c r="D123">
-        <f>(B123+C123)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2373,7 +2536,7 @@
         <v>30</v>
       </c>
       <c r="D124">
-        <f>(B124+C124)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2388,7 +2551,7 @@
         <v>30</v>
       </c>
       <c r="D125">
-        <f>(B125+C125)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
     </row>
@@ -2403,7 +2566,7 @@
         <v>30</v>
       </c>
       <c r="D126">
-        <f>(B126+C126)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2418,7 +2581,7 @@
         <v>30</v>
       </c>
       <c r="D127">
-        <f>(B127+C127)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
     </row>
@@ -2433,7 +2596,7 @@
         <v>30</v>
       </c>
       <c r="D128">
-        <f>(B128+C128)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16.5</v>
       </c>
     </row>
@@ -2448,7 +2611,7 @@
         <v>30</v>
       </c>
       <c r="D129">
-        <f>(B129+C129)/2 -10</f>
+        <f t="shared" si="1"/>
         <v>16.5</v>
       </c>
     </row>
@@ -2463,7 +2626,7 @@
         <v>30</v>
       </c>
       <c r="D130">
-        <f>(B130+C130)/2 -10</f>
+        <f t="shared" ref="D130:D193" si="2">(B130+C130)/2 -10</f>
         <v>14.5</v>
       </c>
     </row>
@@ -2478,7 +2641,7 @@
         <v>30</v>
       </c>
       <c r="D131">
-        <f>(B131+C131)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2493,7 +2656,7 @@
         <v>30</v>
       </c>
       <c r="D132">
-        <f>(B132+C132)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2508,7 +2671,7 @@
         <v>30</v>
       </c>
       <c r="D133">
-        <f>(B133+C133)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -2523,7 +2686,7 @@
         <v>30</v>
       </c>
       <c r="D134">
-        <f>(B134+C134)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2538,7 +2701,7 @@
         <v>30</v>
       </c>
       <c r="D135">
-        <f>(B135+C135)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
@@ -2553,7 +2716,7 @@
         <v>30</v>
       </c>
       <c r="D136">
-        <f>(B136+C136)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2568,7 +2731,7 @@
         <v>30</v>
       </c>
       <c r="D137">
-        <f>(B137+C137)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2583,7 +2746,7 @@
         <v>30</v>
       </c>
       <c r="D138">
-        <f>(B138+C138)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2598,7 +2761,7 @@
         <v>30</v>
       </c>
       <c r="D139">
-        <f>(B139+C139)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2613,7 +2776,7 @@
         <v>30</v>
       </c>
       <c r="D140">
-        <f>(B140+C140)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2628,7 +2791,7 @@
         <v>30</v>
       </c>
       <c r="D141">
-        <f>(B141+C141)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2643,7 +2806,7 @@
         <v>30</v>
       </c>
       <c r="D142">
-        <f>(B142+C142)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2658,7 +2821,7 @@
         <v>30</v>
       </c>
       <c r="D143">
-        <f>(B143+C143)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2673,7 +2836,7 @@
         <v>30</v>
       </c>
       <c r="D144">
-        <f>(B144+C144)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2688,7 +2851,7 @@
         <v>30</v>
       </c>
       <c r="D145">
-        <f>(B145+C145)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -2703,7 +2866,7 @@
         <v>30</v>
       </c>
       <c r="D146">
-        <f>(B146+C146)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2718,7 +2881,7 @@
         <v>30</v>
       </c>
       <c r="D147">
-        <f>(B147+C147)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
@@ -2733,7 +2896,7 @@
         <v>30</v>
       </c>
       <c r="D148">
-        <f>(B148+C148)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2748,7 +2911,7 @@
         <v>30</v>
       </c>
       <c r="D149">
-        <f>(B149+C149)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2763,7 +2926,7 @@
         <v>30</v>
       </c>
       <c r="D150">
-        <f>(B150+C150)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>17.5</v>
       </c>
     </row>
@@ -2778,7 +2941,7 @@
         <v>30</v>
       </c>
       <c r="D151">
-        <f>(B151+C151)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -2793,7 +2956,7 @@
         <v>30</v>
       </c>
       <c r="D152">
-        <f>(B152+C152)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2808,7 +2971,7 @@
         <v>30</v>
       </c>
       <c r="D153">
-        <f>(B153+C153)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>14.5</v>
       </c>
     </row>
@@ -2823,7 +2986,7 @@
         <v>30</v>
       </c>
       <c r="D154">
-        <f>(B154+C154)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2838,7 +3001,7 @@
         <v>30</v>
       </c>
       <c r="D155">
-        <f>(B155+C155)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2853,7 +3016,7 @@
         <v>30</v>
       </c>
       <c r="D156">
-        <f>(B156+C156)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2868,7 +3031,7 @@
         <v>30</v>
       </c>
       <c r="D157">
-        <f>(B157+C157)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2883,7 +3046,7 @@
         <v>30</v>
       </c>
       <c r="D158">
-        <f>(B158+C158)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -2898,7 +3061,7 @@
         <v>30</v>
       </c>
       <c r="D159">
-        <f>(B159+C159)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>17.5</v>
       </c>
     </row>
@@ -2913,7 +3076,7 @@
         <v>30</v>
       </c>
       <c r="D160">
-        <f>(B160+C160)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2928,7 +3091,7 @@
         <v>30</v>
       </c>
       <c r="D161">
-        <f>(B161+C161)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2943,7 +3106,7 @@
         <v>30</v>
       </c>
       <c r="D162">
-        <f>(B162+C162)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2958,7 +3121,7 @@
         <v>30</v>
       </c>
       <c r="D163">
-        <f>(B163+C163)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -2973,7 +3136,7 @@
         <v>30</v>
       </c>
       <c r="D164">
-        <f>(B164+C164)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -2988,7 +3151,7 @@
         <v>30</v>
       </c>
       <c r="D165">
-        <f>(B165+C165)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3003,7 +3166,7 @@
         <v>30</v>
       </c>
       <c r="D166">
-        <f>(B166+C166)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3018,7 +3181,7 @@
         <v>30</v>
       </c>
       <c r="D167">
-        <f>(B167+C167)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3033,7 +3196,7 @@
         <v>30</v>
       </c>
       <c r="D168">
-        <f>(B168+C168)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3048,7 +3211,7 @@
         <v>30</v>
       </c>
       <c r="D169">
-        <f>(B169+C169)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3063,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="D170">
-        <f>(B170+C170)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3078,7 +3241,7 @@
         <v>30</v>
       </c>
       <c r="D171">
-        <f>(B171+C171)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3093,7 +3256,7 @@
         <v>30</v>
       </c>
       <c r="D172">
-        <f>(B172+C172)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3108,7 +3271,7 @@
         <v>30</v>
       </c>
       <c r="D173">
-        <f>(B173+C173)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3123,7 +3286,7 @@
         <v>30</v>
       </c>
       <c r="D174">
-        <f>(B174+C174)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3138,7 +3301,7 @@
         <v>30</v>
       </c>
       <c r="D175">
-        <f>(B175+C175)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3153,7 +3316,7 @@
         <v>30</v>
       </c>
       <c r="D176">
-        <f>(B176+C176)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3168,7 +3331,7 @@
         <v>30</v>
       </c>
       <c r="D177">
-        <f>(B177+C177)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3183,7 +3346,7 @@
         <v>30</v>
       </c>
       <c r="D178">
-        <f>(B178+C178)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3198,7 +3361,7 @@
         <v>30</v>
       </c>
       <c r="D179">
-        <f>(B179+C179)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3213,7 +3376,7 @@
         <v>30</v>
       </c>
       <c r="D180">
-        <f>(B180+C180)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3228,7 +3391,7 @@
         <v>30</v>
       </c>
       <c r="D181">
-        <f>(B181+C181)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3243,7 +3406,7 @@
         <v>30</v>
       </c>
       <c r="D182">
-        <f>(B182+C182)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3258,7 +3421,7 @@
         <v>30</v>
       </c>
       <c r="D183">
-        <f>(B183+C183)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3273,7 +3436,7 @@
         <v>30</v>
       </c>
       <c r="D184">
-        <f>(B184+C184)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3288,7 +3451,7 @@
         <v>30</v>
       </c>
       <c r="D185">
-        <f>(B185+C185)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3303,7 +3466,7 @@
         <v>30</v>
       </c>
       <c r="D186">
-        <f>(B186+C186)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>14.5</v>
       </c>
     </row>
@@ -3318,7 +3481,7 @@
         <v>30</v>
       </c>
       <c r="D187">
-        <f>(B187+C187)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3333,7 +3496,7 @@
         <v>30</v>
       </c>
       <c r="D188">
-        <f>(B188+C188)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -3348,7 +3511,7 @@
         <v>30</v>
       </c>
       <c r="D189">
-        <f>(B189+C189)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3363,7 +3526,7 @@
         <v>30</v>
       </c>
       <c r="D190">
-        <f>(B190+C190)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3378,7 +3541,7 @@
         <v>30</v>
       </c>
       <c r="D191">
-        <f>(B191+C191)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3393,7 +3556,7 @@
         <v>30</v>
       </c>
       <c r="D192">
-        <f>(B192+C192)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3408,7 +3571,7 @@
         <v>30</v>
       </c>
       <c r="D193">
-        <f>(B193+C193)/2 -10</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -3423,7 +3586,7 @@
         <v>30</v>
       </c>
       <c r="D194">
-        <f>(B194+C194)/2 -10</f>
+        <f t="shared" ref="D194:D257" si="3">(B194+C194)/2 -10</f>
         <v>15</v>
       </c>
     </row>
@@ -3438,7 +3601,7 @@
         <v>30</v>
       </c>
       <c r="D195">
-        <f>(B195+C195)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3453,7 +3616,7 @@
         <v>30</v>
       </c>
       <c r="D196">
-        <f>(B196+C196)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3468,7 +3631,7 @@
         <v>30</v>
       </c>
       <c r="D197">
-        <f>(B197+C197)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
@@ -3483,7 +3646,7 @@
         <v>30</v>
       </c>
       <c r="D198">
-        <f>(B198+C198)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
@@ -3498,7 +3661,7 @@
         <v>30</v>
       </c>
       <c r="D199">
-        <f>(B199+C199)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3513,7 +3676,7 @@
         <v>30</v>
       </c>
       <c r="D200">
-        <f>(B200+C200)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3528,7 +3691,7 @@
         <v>30</v>
       </c>
       <c r="D201">
-        <f>(B201+C201)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3543,7 +3706,7 @@
         <v>30</v>
       </c>
       <c r="D202">
-        <f>(B202+C202)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3558,7 +3721,7 @@
         <v>30</v>
       </c>
       <c r="D203">
-        <f>(B203+C203)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3573,7 +3736,7 @@
         <v>30</v>
       </c>
       <c r="D204">
-        <f>(B204+C204)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3588,7 +3751,7 @@
         <v>30</v>
       </c>
       <c r="D205">
-        <f>(B205+C205)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
@@ -3603,7 +3766,7 @@
         <v>30</v>
       </c>
       <c r="D206">
-        <f>(B206+C206)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3618,7 +3781,7 @@
         <v>30</v>
       </c>
       <c r="D207">
-        <f>(B207+C207)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3633,7 +3796,7 @@
         <v>30</v>
       </c>
       <c r="D208">
-        <f>(B208+C208)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3648,7 +3811,7 @@
         <v>30</v>
       </c>
       <c r="D209">
-        <f>(B209+C209)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3663,7 +3826,7 @@
         <v>30</v>
       </c>
       <c r="D210">
-        <f>(B210+C210)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3678,7 +3841,7 @@
         <v>30</v>
       </c>
       <c r="D211">
-        <f>(B211+C211)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3693,7 +3856,7 @@
         <v>30</v>
       </c>
       <c r="D212">
-        <f>(B212+C212)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3708,7 +3871,7 @@
         <v>30</v>
       </c>
       <c r="D213">
-        <f>(B213+C213)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -3723,7 +3886,7 @@
         <v>30</v>
       </c>
       <c r="D214">
-        <f>(B214+C214)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -3738,7 +3901,7 @@
         <v>30</v>
       </c>
       <c r="D215">
-        <f>(B215+C215)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -3753,7 +3916,7 @@
         <v>30</v>
       </c>
       <c r="D216">
-        <f>(B216+C216)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3768,7 +3931,7 @@
         <v>30</v>
       </c>
       <c r="D217">
-        <f>(B217+C217)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3783,7 +3946,7 @@
         <v>30</v>
       </c>
       <c r="D218">
-        <f>(B218+C218)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3798,7 +3961,7 @@
         <v>30</v>
       </c>
       <c r="D219">
-        <f>(B219+C219)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3813,7 +3976,7 @@
         <v>30</v>
       </c>
       <c r="D220">
-        <f>(B220+C220)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3828,7 +3991,7 @@
         <v>30</v>
       </c>
       <c r="D221">
-        <f>(B221+C221)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3843,7 +4006,7 @@
         <v>30</v>
       </c>
       <c r="D222">
-        <f>(B222+C222)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3858,7 +4021,7 @@
         <v>30</v>
       </c>
       <c r="D223">
-        <f>(B223+C223)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3873,7 +4036,7 @@
         <v>30</v>
       </c>
       <c r="D224">
-        <f>(B224+C224)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3888,7 +4051,7 @@
         <v>28.6</v>
       </c>
       <c r="D225">
-        <f>(B225+C225)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.3</v>
       </c>
     </row>
@@ -3903,7 +4066,7 @@
         <v>30</v>
       </c>
       <c r="D226">
-        <f>(B226+C226)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
@@ -3918,7 +4081,7 @@
         <v>30</v>
       </c>
       <c r="D227">
-        <f>(B227+C227)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3933,7 +4096,7 @@
         <v>29</v>
       </c>
       <c r="D228">
-        <f>(B228+C228)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
     </row>
@@ -3948,7 +4111,7 @@
         <v>27.5</v>
       </c>
       <c r="D229">
-        <f>(B229+C229)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.75</v>
       </c>
     </row>
@@ -3963,7 +4126,7 @@
         <v>24.9</v>
       </c>
       <c r="D230">
-        <f>(B230+C230)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.45</v>
       </c>
     </row>
@@ -3978,7 +4141,7 @@
         <v>30</v>
       </c>
       <c r="D231">
-        <f>(B231+C231)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -3993,7 +4156,7 @@
         <v>23.7</v>
       </c>
       <c r="D232">
-        <f>(B232+C232)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>12.850000000000001</v>
       </c>
     </row>
@@ -4008,7 +4171,7 @@
         <v>26.5</v>
       </c>
       <c r="D233">
-        <f>(B233+C233)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.25</v>
       </c>
     </row>
@@ -4023,7 +4186,7 @@
         <v>30</v>
       </c>
       <c r="D234">
-        <f>(B234+C234)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -4038,7 +4201,7 @@
         <v>30</v>
       </c>
       <c r="D235">
-        <f>(B235+C235)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -4053,7 +4216,7 @@
         <v>30</v>
       </c>
       <c r="D236">
-        <f>(B236+C236)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -4068,7 +4231,7 @@
         <v>30</v>
       </c>
       <c r="D237">
-        <f>(B237+C237)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -4083,7 +4246,7 @@
         <v>30</v>
       </c>
       <c r="D238">
-        <f>(B238+C238)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
     </row>
@@ -4098,7 +4261,7 @@
         <v>30</v>
       </c>
       <c r="D239">
-        <f>(B239+C239)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -4113,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="D240">
-        <f>(B240+C240)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -4128,7 +4291,7 @@
         <v>30</v>
       </c>
       <c r="D241">
-        <f>(B241+C241)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -4143,7 +4306,7 @@
         <v>30</v>
       </c>
       <c r="D242">
-        <f>(B242+C242)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>16.5</v>
       </c>
     </row>
@@ -4158,7 +4321,7 @@
         <v>30</v>
       </c>
       <c r="D243">
-        <f>(B243+C243)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.350000000000001</v>
       </c>
     </row>
@@ -4173,7 +4336,7 @@
         <v>30</v>
       </c>
       <c r="D244">
-        <f>(B244+C244)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.45</v>
       </c>
     </row>
@@ -4188,7 +4351,7 @@
         <v>29</v>
       </c>
       <c r="D245">
-        <f>(B245+C245)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -4203,7 +4366,7 @@
         <v>28.6</v>
       </c>
       <c r="D246">
-        <f>(B246+C246)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.25</v>
       </c>
     </row>
@@ -4218,7 +4381,7 @@
         <v>26.4</v>
       </c>
       <c r="D247">
-        <f>(B247+C247)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>12.899999999999999</v>
       </c>
     </row>
@@ -4233,7 +4396,7 @@
         <v>27.6</v>
       </c>
       <c r="D248">
-        <f>(B248+C248)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>12.450000000000003</v>
       </c>
     </row>
@@ -4248,7 +4411,7 @@
         <v>27.1</v>
       </c>
       <c r="D249">
-        <f>(B249+C249)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.399999999999999</v>
       </c>
     </row>
@@ -4263,7 +4426,7 @@
         <v>30</v>
       </c>
       <c r="D250">
-        <f>(B250+C250)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.8</v>
       </c>
     </row>
@@ -4278,7 +4441,7 @@
         <v>29.5</v>
       </c>
       <c r="D251">
-        <f>(B251+C251)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.600000000000001</v>
       </c>
     </row>
@@ -4293,7 +4456,7 @@
         <v>29.8</v>
       </c>
       <c r="D252">
-        <f>(B252+C252)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.600000000000001</v>
       </c>
     </row>
@@ -4308,7 +4471,7 @@
         <v>30</v>
       </c>
       <c r="D253">
-        <f>(B253+C253)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.399999999999999</v>
       </c>
     </row>
@@ -4323,7 +4486,7 @@
         <v>30</v>
       </c>
       <c r="D254">
-        <f>(B254+C254)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.3</v>
       </c>
     </row>
@@ -4338,7 +4501,7 @@
         <v>30</v>
       </c>
       <c r="D255">
-        <f>(B255+C255)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>13.149999999999999</v>
       </c>
     </row>
@@ -4353,7 +4516,7 @@
         <v>30</v>
       </c>
       <c r="D256">
-        <f>(B256+C256)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
     </row>
@@ -4368,7 +4531,7 @@
         <v>30</v>
       </c>
       <c r="D257">
-        <f>(B257+C257)/2 -10</f>
+        <f t="shared" si="3"/>
         <v>15.600000000000001</v>
       </c>
     </row>
@@ -4383,7 +4546,7 @@
         <v>30</v>
       </c>
       <c r="D258">
-        <f>(B258+C258)/2 -10</f>
+        <f t="shared" ref="D258:D321" si="4">(B258+C258)/2 -10</f>
         <v>14.600000000000001</v>
       </c>
     </row>
@@ -4398,7 +4561,7 @@
         <v>30</v>
       </c>
       <c r="D259">
-        <f>(B259+C259)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -4413,7 +4576,7 @@
         <v>30</v>
       </c>
       <c r="D260">
-        <f>(B260+C260)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.100000000000001</v>
       </c>
     </row>
@@ -4428,7 +4591,7 @@
         <v>30</v>
       </c>
       <c r="D261">
-        <f>(B261+C261)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.350000000000001</v>
       </c>
     </row>
@@ -4443,7 +4606,7 @@
         <v>30</v>
       </c>
       <c r="D262">
-        <f>(B262+C262)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.55</v>
       </c>
     </row>
@@ -4458,7 +4621,7 @@
         <v>29.9</v>
       </c>
       <c r="D263">
-        <f>(B263+C263)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.899999999999999</v>
       </c>
     </row>
@@ -4473,7 +4636,7 @@
         <v>28.3</v>
       </c>
       <c r="D264">
-        <f>(B264+C264)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
     </row>
@@ -4488,7 +4651,7 @@
         <v>29.4</v>
       </c>
       <c r="D265">
-        <f>(B265+C265)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>12.399999999999999</v>
       </c>
     </row>
@@ -4503,7 +4666,7 @@
         <v>30</v>
       </c>
       <c r="D266">
-        <f>(B266+C266)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
     </row>
@@ -4518,7 +4681,7 @@
         <v>29.7</v>
       </c>
       <c r="D267">
-        <f>(B267+C267)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.45</v>
       </c>
     </row>
@@ -4533,7 +4696,7 @@
         <v>30</v>
       </c>
       <c r="D268">
-        <f>(B268+C268)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.05</v>
       </c>
     </row>
@@ -4548,7 +4711,7 @@
         <v>30</v>
       </c>
       <c r="D269">
-        <f>(B269+C269)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.149999999999999</v>
       </c>
     </row>
@@ -4563,7 +4726,7 @@
         <v>30</v>
       </c>
       <c r="D270">
-        <f>(B270+C270)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.2</v>
       </c>
     </row>
@@ -4578,7 +4741,7 @@
         <v>30</v>
       </c>
       <c r="D271">
-        <f>(B271+C271)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.8</v>
       </c>
     </row>
@@ -4593,7 +4756,7 @@
         <v>30</v>
       </c>
       <c r="D272">
-        <f>(B272+C272)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.600000000000001</v>
       </c>
     </row>
@@ -4608,7 +4771,7 @@
         <v>30</v>
       </c>
       <c r="D273">
-        <f>(B273+C273)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.95</v>
       </c>
     </row>
@@ -4623,7 +4786,7 @@
         <v>30</v>
       </c>
       <c r="D274">
-        <f>(B274+C274)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.649999999999999</v>
       </c>
     </row>
@@ -4638,7 +4801,7 @@
         <v>30</v>
       </c>
       <c r="D275">
-        <f>(B275+C275)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.350000000000001</v>
       </c>
     </row>
@@ -4653,7 +4816,7 @@
         <v>30</v>
       </c>
       <c r="D276">
-        <f>(B276+C276)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.899999999999999</v>
       </c>
     </row>
@@ -4668,7 +4831,7 @@
         <v>30</v>
       </c>
       <c r="D277">
-        <f>(B277+C277)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.649999999999999</v>
       </c>
     </row>
@@ -4683,7 +4846,7 @@
         <v>30</v>
       </c>
       <c r="D278">
-        <f>(B278+C278)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.100000000000001</v>
       </c>
     </row>
@@ -4698,7 +4861,7 @@
         <v>30</v>
       </c>
       <c r="D279">
-        <f>(B279+C279)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.7</v>
       </c>
     </row>
@@ -4713,7 +4876,7 @@
         <v>28.1</v>
       </c>
       <c r="D280">
-        <f>(B280+C280)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.600000000000001</v>
       </c>
     </row>
@@ -4728,7 +4891,7 @@
         <v>30</v>
       </c>
       <c r="D281">
-        <f>(B281+C281)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.05</v>
       </c>
     </row>
@@ -4743,7 +4906,7 @@
         <v>30</v>
       </c>
       <c r="D282">
-        <f>(B282+C282)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.55</v>
       </c>
     </row>
@@ -4758,7 +4921,7 @@
         <v>30</v>
       </c>
       <c r="D283">
-        <f>(B283+C283)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -4773,7 +4936,7 @@
         <v>30</v>
       </c>
       <c r="D284">
-        <f>(B284+C284)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.649999999999999</v>
       </c>
     </row>
@@ -4788,7 +4951,7 @@
         <v>30</v>
       </c>
       <c r="D285">
-        <f>(B285+C285)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.850000000000001</v>
       </c>
     </row>
@@ -4803,7 +4966,7 @@
         <v>30</v>
       </c>
       <c r="D286">
-        <f>(B286+C286)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.95</v>
       </c>
     </row>
@@ -4818,7 +4981,7 @@
         <v>30</v>
       </c>
       <c r="D287">
-        <f>(B287+C287)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.95</v>
       </c>
       <c r="S287" s="8"/>
@@ -4835,7 +4998,7 @@
         <v>30</v>
       </c>
       <c r="D288">
-        <f>(B288+C288)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.649999999999999</v>
       </c>
       <c r="S288" s="8"/>
@@ -4852,7 +5015,7 @@
         <v>30</v>
       </c>
       <c r="D289">
-        <f>(B289+C289)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.75</v>
       </c>
       <c r="S289" s="8"/>
@@ -4869,7 +5032,7 @@
         <v>30</v>
       </c>
       <c r="D290">
-        <f>(B290+C290)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.149999999999999</v>
       </c>
       <c r="S290" s="8"/>
@@ -4886,7 +5049,7 @@
         <v>30</v>
       </c>
       <c r="D291">
-        <f>(B291+C291)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.100000000000001</v>
       </c>
       <c r="S291" s="8"/>
@@ -4903,7 +5066,7 @@
         <v>30</v>
       </c>
       <c r="D292">
-        <f>(B292+C292)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S292" s="8"/>
@@ -4920,7 +5083,7 @@
         <v>30</v>
       </c>
       <c r="D293">
-        <f>(B293+C293)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>13.95</v>
       </c>
       <c r="S293" s="8"/>
@@ -4937,7 +5100,7 @@
         <v>30</v>
       </c>
       <c r="D294">
-        <f>(B294+C294)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.7</v>
       </c>
       <c r="S294" s="8"/>
@@ -4954,7 +5117,7 @@
         <v>30</v>
       </c>
       <c r="D295">
-        <f>(B295+C295)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.8</v>
       </c>
       <c r="S295" s="8"/>
@@ -4971,7 +5134,7 @@
         <v>30</v>
       </c>
       <c r="D296">
-        <f>(B296+C296)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.3</v>
       </c>
       <c r="S296" s="8"/>
@@ -4988,7 +5151,7 @@
         <v>30</v>
       </c>
       <c r="D297">
-        <f>(B297+C297)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.100000000000001</v>
       </c>
       <c r="S297" s="8"/>
@@ -5005,7 +5168,7 @@
         <v>29.2</v>
       </c>
       <c r="D298">
-        <f>(B298+C298)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.549999999999997</v>
       </c>
       <c r="S298" s="8"/>
@@ -5022,7 +5185,7 @@
         <v>30</v>
       </c>
       <c r="D299">
-        <f>(B299+C299)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.100000000000001</v>
       </c>
       <c r="S299" s="8"/>
@@ -5039,7 +5202,7 @@
         <v>30</v>
       </c>
       <c r="D300">
-        <f>(B300+C300)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>16.2</v>
       </c>
       <c r="S300" s="8"/>
@@ -5058,7 +5221,7 @@
         <v>30</v>
       </c>
       <c r="D301">
-        <f>(B301+C301)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="S301" s="8"/>
@@ -5077,7 +5240,7 @@
         <v>30</v>
       </c>
       <c r="D302">
-        <f>(B302+C302)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.95</v>
       </c>
       <c r="S302" s="8"/>
@@ -5096,7 +5259,7 @@
         <v>29.3</v>
       </c>
       <c r="D303">
-        <f>(B303+C303)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S303" s="8"/>
@@ -5115,7 +5278,7 @@
         <v>29.6</v>
       </c>
       <c r="D304">
-        <f>(B304+C304)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.75</v>
       </c>
       <c r="S304" s="8"/>
@@ -5134,7 +5297,7 @@
         <v>30</v>
       </c>
       <c r="D305">
-        <f>(B305+C305)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.05</v>
       </c>
       <c r="S305" s="8"/>
@@ -5153,7 +5316,7 @@
         <v>30</v>
       </c>
       <c r="D306">
-        <f>(B306+C306)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.55</v>
       </c>
       <c r="S306" s="8"/>
@@ -5172,7 +5335,7 @@
         <v>30</v>
       </c>
       <c r="D307">
-        <f>(B307+C307)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.600000000000001</v>
       </c>
       <c r="S307" s="8"/>
@@ -5191,7 +5354,7 @@
         <v>30</v>
       </c>
       <c r="D308">
-        <f>(B308+C308)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.5</v>
       </c>
       <c r="S308" s="8"/>
@@ -5210,7 +5373,7 @@
         <v>30</v>
       </c>
       <c r="D309">
-        <f>(B309+C309)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S309" s="8"/>
@@ -5229,7 +5392,7 @@
         <v>30</v>
       </c>
       <c r="D310">
-        <f>(B310+C310)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.55</v>
       </c>
       <c r="S310" s="8"/>
@@ -5248,7 +5411,7 @@
         <v>30</v>
       </c>
       <c r="D311">
-        <f>(B311+C311)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="S311" s="8"/>
@@ -5267,7 +5430,7 @@
         <v>30</v>
       </c>
       <c r="D312">
-        <f>(B312+C312)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>14.850000000000001</v>
       </c>
       <c r="S312" s="8"/>
@@ -5286,7 +5449,7 @@
         <v>30</v>
       </c>
       <c r="D313">
-        <f>(B313+C313)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.95</v>
       </c>
       <c r="S313" s="8"/>
@@ -5305,7 +5468,7 @@
         <v>30</v>
       </c>
       <c r="D314">
-        <f>(B314+C314)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.55</v>
       </c>
       <c r="S314" s="8"/>
@@ -5322,7 +5485,7 @@
         <v>30</v>
       </c>
       <c r="D315">
-        <f>(B315+C315)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.8</v>
       </c>
       <c r="S315" s="8"/>
@@ -5339,7 +5502,7 @@
         <v>30</v>
       </c>
       <c r="D316">
-        <f>(B316+C316)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.149999999999999</v>
       </c>
       <c r="S316" s="8"/>
@@ -5356,7 +5519,7 @@
         <v>30</v>
       </c>
       <c r="D317">
-        <f>(B317+C317)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
@@ -5371,7 +5534,7 @@
         <v>30</v>
       </c>
       <c r="D318">
-        <f>(B318+C318)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>16.05</v>
       </c>
     </row>
@@ -5386,7 +5549,7 @@
         <v>30</v>
       </c>
       <c r="D319">
-        <f>(B319+C319)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
@@ -5401,7 +5564,7 @@
         <v>30</v>
       </c>
       <c r="D320">
-        <f>(B320+C320)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
     </row>
@@ -5416,7 +5579,7 @@
         <v>30</v>
       </c>
       <c r="D321">
-        <f>(B321+C321)/2 -10</f>
+        <f t="shared" si="4"/>
         <v>15.850000000000001</v>
       </c>
     </row>
@@ -5431,7 +5594,7 @@
         <v>30</v>
       </c>
       <c r="D322">
-        <f>(B322+C322)/2 -10</f>
+        <f t="shared" ref="D322:D330" si="5">(B322+C322)/2 -10</f>
         <v>14.850000000000001</v>
       </c>
     </row>
@@ -5446,7 +5609,7 @@
         <v>30</v>
       </c>
       <c r="D323">
-        <f>(B323+C323)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>15.100000000000001</v>
       </c>
       <c r="P323" s="8"/>
@@ -5463,7 +5626,7 @@
         <v>30</v>
       </c>
       <c r="D324">
-        <f>(B324+C324)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>15.75</v>
       </c>
       <c r="P324" s="8"/>
@@ -5480,7 +5643,7 @@
         <v>30</v>
       </c>
       <c r="D325">
-        <f>(B325+C325)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>14.8</v>
       </c>
       <c r="P325" s="8"/>
@@ -5497,7 +5660,7 @@
         <v>30</v>
       </c>
       <c r="D326">
-        <f>(B326+C326)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>15.95</v>
       </c>
       <c r="P326" s="8"/>
@@ -5514,7 +5677,7 @@
         <v>28.9</v>
       </c>
       <c r="D327">
-        <f>(B327+C327)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>14.899999999999999</v>
       </c>
       <c r="P327" s="8"/>
@@ -5531,7 +5694,7 @@
         <v>28.1</v>
       </c>
       <c r="D328">
-        <f>(B328+C328)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>13.75</v>
       </c>
       <c r="P328" s="8"/>
@@ -5548,7 +5711,7 @@
         <v>30</v>
       </c>
       <c r="D329">
-        <f>(B329+C329)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>15.3</v>
       </c>
       <c r="P329" s="8"/>
@@ -5565,7 +5728,7 @@
         <v>30</v>
       </c>
       <c r="D330">
-        <f>(B330+C330)/2 -10</f>
+        <f t="shared" si="5"/>
         <v>15.350000000000001</v>
       </c>
       <c r="P330" s="8"/>
@@ -5581,7 +5744,7 @@
       <c r="C331">
         <v>30</v>
       </c>
-      <c r="D331">
+      <c r="D331" s="20">
         <f>(B331+C331)/2 -10</f>
         <v>16</v>
       </c>
@@ -5589,72 +5752,743 @@
       <c r="Q331" s="8"/>
     </row>
     <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A332" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B332" s="18">
+        <v>19.5</v>
+      </c>
+      <c r="C332" s="19">
+        <v>32.6</v>
+      </c>
+      <c r="D332" s="20">
+        <f t="shared" ref="D332:D378" si="6">(B332+C332)/2 -10</f>
+        <v>16.05</v>
+      </c>
       <c r="P332" s="8"/>
       <c r="Q332" s="8"/>
     </row>
     <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A333" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B333" s="18">
+        <v>20.3</v>
+      </c>
+      <c r="C333" s="19">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D333" s="20">
+        <f t="shared" si="6"/>
+        <v>17.25</v>
+      </c>
       <c r="P333" s="8"/>
       <c r="Q333" s="8"/>
     </row>
     <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A334" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B334" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="C334" s="19">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="D334" s="20">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
       <c r="P334" s="8"/>
       <c r="Q334" s="8"/>
     </row>
     <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A335" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B335" s="18">
+        <v>21.6</v>
+      </c>
+      <c r="C335" s="19">
+        <v>34.4</v>
+      </c>
+      <c r="D335" s="20">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
       <c r="P335" s="8"/>
       <c r="Q335" s="8"/>
     </row>
     <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A336" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B336" s="18">
+        <v>20.3</v>
+      </c>
+      <c r="C336" s="19">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="D336" s="20">
+        <f t="shared" si="6"/>
+        <v>17.5</v>
+      </c>
       <c r="P336" s="8"/>
       <c r="Q336" s="8"/>
     </row>
-    <row r="337" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A337" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B337" s="18">
+        <v>22.7</v>
+      </c>
+      <c r="C337" s="19">
+        <v>31.7</v>
+      </c>
+      <c r="D337" s="20">
+        <f t="shared" si="6"/>
+        <v>17.2</v>
+      </c>
       <c r="P337" s="8"/>
       <c r="Q337" s="8"/>
     </row>
-    <row r="338" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A338" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B338" s="18">
+        <v>22.2</v>
+      </c>
+      <c r="C338" s="19">
+        <v>34.4</v>
+      </c>
+      <c r="D338" s="20">
+        <f t="shared" si="6"/>
+        <v>18.299999999999997</v>
+      </c>
       <c r="P338" s="8"/>
       <c r="Q338" s="8"/>
     </row>
-    <row r="339" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A339" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B339" s="18">
+        <v>21.4</v>
+      </c>
+      <c r="C339" s="19">
+        <v>33.4</v>
+      </c>
+      <c r="D339" s="20">
+        <f t="shared" si="6"/>
+        <v>17.399999999999999</v>
+      </c>
       <c r="P339" s="8"/>
       <c r="Q339" s="8"/>
     </row>
-    <row r="340" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A340" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B340" s="18">
+        <v>21.3</v>
+      </c>
+      <c r="C340" s="19">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D340" s="20">
+        <f t="shared" si="6"/>
+        <v>18.299999999999997</v>
+      </c>
       <c r="P340" s="8"/>
       <c r="Q340" s="8"/>
     </row>
-    <row r="341" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A341" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B341" s="18">
+        <v>21.1</v>
+      </c>
+      <c r="C341" s="19">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="D341" s="20">
+        <f t="shared" si="6"/>
+        <v>18.95</v>
+      </c>
       <c r="P341" s="8"/>
       <c r="Q341" s="8"/>
     </row>
-    <row r="342" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A342" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B342" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="C342" s="19">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="D342" s="20">
+        <f t="shared" si="6"/>
+        <v>19.25</v>
+      </c>
       <c r="P342" s="8"/>
       <c r="Q342" s="8"/>
     </row>
-    <row r="343" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A343" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B343" s="18">
+        <v>21.9</v>
+      </c>
+      <c r="C343" s="19">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D343" s="20">
+        <f t="shared" si="6"/>
+        <v>19.55</v>
+      </c>
       <c r="P343" s="8"/>
       <c r="Q343" s="8"/>
     </row>
-    <row r="344" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A344" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B344" s="18">
+        <v>24.7</v>
+      </c>
+      <c r="C344" s="19">
+        <v>36</v>
+      </c>
+      <c r="D344" s="20">
+        <f t="shared" si="6"/>
+        <v>20.350000000000001</v>
+      </c>
       <c r="P344" s="8"/>
       <c r="Q344" s="8"/>
     </row>
-    <row r="345" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A345" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B345" s="18">
+        <v>24.4</v>
+      </c>
+      <c r="C345" s="19">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="D345" s="20">
+        <f t="shared" si="6"/>
+        <v>20.8</v>
+      </c>
       <c r="P345" s="8"/>
       <c r="Q345" s="8"/>
     </row>
-    <row r="346" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A346" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B346" s="18">
+        <v>22.6</v>
+      </c>
+      <c r="C346" s="19">
+        <v>37.9</v>
+      </c>
+      <c r="D346" s="20">
+        <f t="shared" si="6"/>
+        <v>20.25</v>
+      </c>
       <c r="P346" s="8"/>
       <c r="Q346" s="8"/>
     </row>
-    <row r="347" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A347" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B347" s="18">
+        <v>21.6</v>
+      </c>
+      <c r="C347" s="19">
+        <v>35.5</v>
+      </c>
+      <c r="D347" s="20">
+        <f t="shared" si="6"/>
+        <v>18.55</v>
+      </c>
       <c r="P347" s="8"/>
       <c r="Q347" s="8"/>
     </row>
-    <row r="348" spans="16:17" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A348" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B348" s="18">
+        <v>20.6</v>
+      </c>
+      <c r="C348" s="19">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="D348" s="20">
+        <f t="shared" si="6"/>
+        <v>16.95</v>
+      </c>
       <c r="P348" s="8"/>
       <c r="Q348" s="8"/>
+    </row>
+    <row r="349" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A349" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B349" s="18">
+        <v>21.5</v>
+      </c>
+      <c r="C349" s="19">
+        <v>34.4</v>
+      </c>
+      <c r="D349" s="20">
+        <f t="shared" si="6"/>
+        <v>17.95</v>
+      </c>
+    </row>
+    <row r="350" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A350" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B350" s="18">
+        <v>22.4</v>
+      </c>
+      <c r="C350" s="19">
+        <v>33.4</v>
+      </c>
+      <c r="D350" s="20">
+        <f t="shared" si="6"/>
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="351" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A351" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B351" s="18">
+        <v>22.7</v>
+      </c>
+      <c r="C351" s="19">
+        <v>34.1</v>
+      </c>
+      <c r="D351" s="20">
+        <f t="shared" si="6"/>
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="352" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A352" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B352" s="18">
+        <v>20.7</v>
+      </c>
+      <c r="C352" s="19">
+        <v>34.5</v>
+      </c>
+      <c r="D352" s="20">
+        <f t="shared" si="6"/>
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A353" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B353" s="18">
+        <v>22.1</v>
+      </c>
+      <c r="C353" s="19">
+        <v>35.4</v>
+      </c>
+      <c r="D353" s="20">
+        <f t="shared" si="6"/>
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A354" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B354" s="18">
+        <v>21.2</v>
+      </c>
+      <c r="C354" s="19">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D354" s="20">
+        <f t="shared" si="6"/>
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A355" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B355" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="C355" s="19">
+        <v>37.4</v>
+      </c>
+      <c r="D355" s="20">
+        <f t="shared" si="6"/>
+        <v>19.850000000000001</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A356" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B356" s="18">
+        <v>22.1</v>
+      </c>
+      <c r="C356" s="19">
+        <v>32.9</v>
+      </c>
+      <c r="D356" s="20">
+        <f t="shared" si="6"/>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A357" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B357" s="18">
+        <v>21.8</v>
+      </c>
+      <c r="C357" s="19">
+        <v>26</v>
+      </c>
+      <c r="D357" s="20">
+        <f t="shared" si="6"/>
+        <v>13.899999999999999</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A358" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B358" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="C358" s="19">
+        <v>28.1</v>
+      </c>
+      <c r="D358" s="20">
+        <f t="shared" si="6"/>
+        <v>15.200000000000003</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A359" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B359" s="18">
+        <v>22.1</v>
+      </c>
+      <c r="C359" s="19">
+        <v>31.5</v>
+      </c>
+      <c r="D359" s="20">
+        <f t="shared" si="6"/>
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A360" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B360" s="18">
+        <v>23.2</v>
+      </c>
+      <c r="C360" s="19">
+        <v>33.1</v>
+      </c>
+      <c r="D360" s="20">
+        <f t="shared" si="6"/>
+        <v>18.149999999999999</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A361" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B361" s="18">
+        <v>23.5</v>
+      </c>
+      <c r="C361" s="19">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D361" s="20">
+        <f t="shared" si="6"/>
+        <v>18.649999999999999</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A362" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B362" s="18">
+        <v>23.1</v>
+      </c>
+      <c r="C362" s="19">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D362" s="20">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B363" s="18">
+        <v>23.2</v>
+      </c>
+      <c r="C363" s="19">
+        <v>36</v>
+      </c>
+      <c r="D363" s="20">
+        <f t="shared" si="6"/>
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B364" s="18">
+        <v>24.8</v>
+      </c>
+      <c r="C364" s="19">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D364" s="20">
+        <f t="shared" si="6"/>
+        <v>19.799999999999997</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B365" s="18">
+        <v>23.7</v>
+      </c>
+      <c r="C365" s="19">
+        <v>33.9</v>
+      </c>
+      <c r="D365" s="20">
+        <f t="shared" si="6"/>
+        <v>18.799999999999997</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B366" s="18">
+        <v>22.8</v>
+      </c>
+      <c r="C366" s="19">
+        <v>33.1</v>
+      </c>
+      <c r="D366" s="20">
+        <f t="shared" si="6"/>
+        <v>17.950000000000003</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B367" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="C367" s="19">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D367" s="20">
+        <f t="shared" si="6"/>
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A368" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B368" s="18">
+        <v>22.5</v>
+      </c>
+      <c r="C368" s="19">
+        <v>34</v>
+      </c>
+      <c r="D368" s="20">
+        <f t="shared" si="6"/>
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A369" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B369" s="18">
+        <v>22.4</v>
+      </c>
+      <c r="C369" s="19">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D369" s="20">
+        <f t="shared" si="6"/>
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A370" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B370" s="18">
+        <v>23</v>
+      </c>
+      <c r="C370" s="19">
+        <v>34.6</v>
+      </c>
+      <c r="D370" s="20">
+        <f t="shared" si="6"/>
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A371" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B371" s="18">
+        <v>22.5</v>
+      </c>
+      <c r="C371" s="19">
+        <v>36.1</v>
+      </c>
+      <c r="D371" s="20">
+        <f t="shared" si="6"/>
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B372" s="18">
+        <v>21.2</v>
+      </c>
+      <c r="C372" s="19">
+        <v>31.5</v>
+      </c>
+      <c r="D372" s="20">
+        <f t="shared" si="6"/>
+        <v>16.350000000000001</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B373" s="18">
+        <v>21.7</v>
+      </c>
+      <c r="C373" s="19">
+        <v>30.7</v>
+      </c>
+      <c r="D373" s="20">
+        <f t="shared" si="6"/>
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B374" s="18">
+        <v>22.8</v>
+      </c>
+      <c r="C374" s="19">
+        <v>31.1</v>
+      </c>
+      <c r="D374" s="20">
+        <f t="shared" si="6"/>
+        <v>16.950000000000003</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A375" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B375" s="18">
+        <v>22.3</v>
+      </c>
+      <c r="C375" s="19">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="D375" s="20">
+        <f t="shared" si="6"/>
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B376" s="18">
+        <v>21.3</v>
+      </c>
+      <c r="C376" s="19">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="D376" s="20">
+        <f t="shared" si="6"/>
+        <v>17.299999999999997</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A377" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B377" s="18">
+        <v>21.4</v>
+      </c>
+      <c r="C377" s="19">
+        <v>34.4</v>
+      </c>
+      <c r="D377" s="20">
+        <f t="shared" si="6"/>
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A378" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B378" s="18">
+        <v>22.9</v>
+      </c>
+      <c r="C378" s="19">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="D378" s="20">
+        <f t="shared" si="6"/>
+        <v>19.099999999999998</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D312" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -5672,7 +6506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDECEE7B-FF86-4CEE-837E-2A35318C4507}">
-  <dimension ref="B4:G18"/>
+  <dimension ref="B4:Z51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" customWidth="1"/>
@@ -5684,7 +6518,7 @@
     <col min="7" max="7" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
         <v>7</v>
       </c>
@@ -5701,7 +6535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
@@ -5718,8 +6552,11 @@
         <f t="shared" ref="G5:G18" si="0">(E5+F5)/2 -10</f>
         <v>14.95</v>
       </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J5" s="4"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+    </row>
+    <row r="6" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C6" s="14" t="s">
         <v>9</v>
       </c>
@@ -5736,8 +6573,11 @@
         <f t="shared" si="0"/>
         <v>14.649999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J6" s="4"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+    </row>
+    <row r="7" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C7" s="14" t="s">
         <v>9</v>
       </c>
@@ -5754,8 +6594,11 @@
         <f t="shared" si="0"/>
         <v>14.75</v>
       </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J7" s="4"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+    </row>
+    <row r="8" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
@@ -5772,8 +6615,11 @@
         <f t="shared" si="0"/>
         <v>15.149999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J8" s="4"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+    </row>
+    <row r="9" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C9" s="14" t="s">
         <v>9</v>
       </c>
@@ -5790,8 +6636,11 @@
         <f t="shared" si="0"/>
         <v>14.100000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J9" s="4"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+    </row>
+    <row r="10" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C10" s="14" t="s">
         <v>9</v>
       </c>
@@ -5808,8 +6657,11 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J10" s="4"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+    </row>
+    <row r="11" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C11" s="14" t="s">
         <v>9</v>
       </c>
@@ -5826,8 +6678,11 @@
         <f t="shared" si="0"/>
         <v>13.95</v>
       </c>
-    </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J11" s="4"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+    </row>
+    <row r="12" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C12" s="14" t="s">
         <v>9</v>
       </c>
@@ -5844,8 +6699,11 @@
         <f t="shared" si="0"/>
         <v>15.7</v>
       </c>
-    </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J12" s="4"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+    </row>
+    <row r="13" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
@@ -5862,8 +6720,11 @@
         <f t="shared" si="0"/>
         <v>14.8</v>
       </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J13" s="4"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+    </row>
+    <row r="14" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C14" s="14" t="s">
         <v>9</v>
       </c>
@@ -5880,8 +6741,11 @@
         <f t="shared" si="0"/>
         <v>14.3</v>
       </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J14" s="4"/>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="8"/>
+    </row>
+    <row r="15" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C15" s="14" t="s">
         <v>9</v>
       </c>
@@ -5898,8 +6762,11 @@
         <f t="shared" si="0"/>
         <v>15.100000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J15" s="4"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+    </row>
+    <row r="16" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C16" s="14" t="s">
         <v>9</v>
       </c>
@@ -5916,8 +6783,11 @@
         <f t="shared" si="0"/>
         <v>15.549999999999997</v>
       </c>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J16" s="4"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>9</v>
       </c>
@@ -5934,8 +6804,11 @@
         <f t="shared" si="0"/>
         <v>17.450000000000003</v>
       </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="J17" s="4"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C18" s="14" t="s">
         <v>9</v>
       </c>
@@ -5952,6 +6825,174 @@
         <f t="shared" si="0"/>
         <v>17.95</v>
       </c>
+      <c r="J18" s="4"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="8"/>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J19" s="4"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J20" s="4"/>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8"/>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J21" s="4"/>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8"/>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J22" s="4"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J23" s="4"/>
+      <c r="Y23" s="8"/>
+      <c r="Z23" s="8"/>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J24" s="4"/>
+      <c r="Y24" s="8"/>
+      <c r="Z24" s="8"/>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J25" s="4"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J26" s="4"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J27" s="4"/>
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8"/>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J28" s="4"/>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8"/>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J29" s="4"/>
+      <c r="Y29" s="8"/>
+      <c r="Z29" s="8"/>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J30" s="4"/>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="8"/>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J31" s="4"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8"/>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="J32" s="4"/>
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="8"/>
+    </row>
+    <row r="33" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J33" s="4"/>
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8"/>
+    </row>
+    <row r="34" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J34" s="4"/>
+      <c r="Y34" s="8"/>
+      <c r="Z34" s="8"/>
+    </row>
+    <row r="35" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J35" s="4"/>
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8"/>
+    </row>
+    <row r="36" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J36" s="4"/>
+      <c r="Y36" s="8"/>
+      <c r="Z36" s="8"/>
+    </row>
+    <row r="37" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J37" s="4"/>
+      <c r="Y37" s="8"/>
+      <c r="Z37" s="8"/>
+    </row>
+    <row r="38" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J38" s="4"/>
+      <c r="Y38" s="8"/>
+      <c r="Z38" s="8"/>
+    </row>
+    <row r="39" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J39" s="4"/>
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="8"/>
+    </row>
+    <row r="40" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J40" s="4"/>
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8"/>
+    </row>
+    <row r="41" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J41" s="4"/>
+      <c r="Y41" s="8"/>
+      <c r="Z41" s="8"/>
+    </row>
+    <row r="42" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J42" s="4"/>
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="8"/>
+    </row>
+    <row r="43" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J43" s="4"/>
+      <c r="Y43" s="8"/>
+      <c r="Z43" s="8"/>
+    </row>
+    <row r="44" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J44" s="4"/>
+      <c r="Y44" s="8"/>
+      <c r="Z44" s="8"/>
+    </row>
+    <row r="45" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J45" s="4"/>
+      <c r="Y45" s="8"/>
+      <c r="Z45" s="8"/>
+    </row>
+    <row r="46" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J46" s="4"/>
+      <c r="Y46" s="8"/>
+      <c r="Z46" s="8"/>
+    </row>
+    <row r="47" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J47" s="4"/>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8"/>
+    </row>
+    <row r="48" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J48" s="4"/>
+      <c r="Y48" s="8"/>
+      <c r="Z48" s="8"/>
+    </row>
+    <row r="49" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J49" s="4"/>
+      <c r="Y49" s="8"/>
+      <c r="Z49" s="8"/>
+    </row>
+    <row r="50" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J50" s="4"/>
+      <c r="Y50" s="8"/>
+      <c r="Z50" s="8"/>
+    </row>
+    <row r="51" spans="10:26" x14ac:dyDescent="0.3">
+      <c r="J51" s="4"/>
+      <c r="Y51" s="8"/>
+      <c r="Z51" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
